--- a/samples/arabic_main_fake_grades.xlsx
+++ b/samples/arabic_main_fake_grades.xlsx
@@ -54,14 +54,14 @@
     <t xml:space="preserve">هبة سمير نبيل رافت</t>
   </si>
   <si>
-    <t/>
+    <t xml:space="preserve">سعيد حميد سلطان عواد</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -85,6 +85,11 @@
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.500000"/>
+      <color indexed="64"/>
+      <name val="Liberation Sans"/>
     </font>
   </fonts>
   <fills count="5">
@@ -143,7 +148,7 @@
     <xf fontId="2" fillId="3" borderId="1" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="3" fillId="4" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -152,6 +157,9 @@
     <xf fontId="3" fillId="4" borderId="0" numFmtId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -769,11 +777,14 @@
       </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="B11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>12</v>
+      <c r="B11" s="4">
+        <v>30</v>
+      </c>
+      <c r="C11" s="4">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
